--- a/output/pdf_financials_xlsx/URB.A.xlsx
+++ b/output/pdf_financials_xlsx/URB.A.xlsx
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.049514</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.058105</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-123.095147</v>
+        <v>-123.144661</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.038384</v>
+        <v>-0.019721</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-123.095147</v>
+        <v>-123.144661</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.038384</v>
+        <v>-0.019721</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.38709</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.268579</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.341421</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>18.639615</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.7251649999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1998,19 +1998,19 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.38709</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.268579</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.341421</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>18.639615</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.7251649999999999</v>
       </c>
     </row>
     <row r="37">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -33394,7 +33394,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" s="5" t="n">

--- a/output/pdf_financials_xlsx/URB.A.xlsx
+++ b/output/pdf_financials_xlsx/URB.A.xlsx
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3.605128</v>
+        <v>3.626028</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2.341056</v>
+        <v>2.361056</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.770159</v>
+        <v>2.819224</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.264604</v>
+        <v>2.312115</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>11.155327</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>4.619958</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>14.771874</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>43.991126</v>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
@@ -5533,13 +5533,13 @@
         </is>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>88.481701</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>28.06555</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>22.149643</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -17315,7 +17315,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -20877,7 +20881,11 @@
           <t>Provision for future income taxes</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -21567,7 +21575,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E224" s="5" t="n">
         <v>11.155327</v>
       </c>
@@ -25484,7 +25496,11 @@
           <t>Provision for future income taxes</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E281" s="5" t="n">
         <v>-19.2</v>
       </c>
@@ -31411,7 +31427,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E368" s="5" t="n">
         <v>0.0209</v>
       </c>
